--- a/education_forms/039_science_project_report_upload_form--education_forms.xlsx
+++ b/education_forms/039_science_project_report_upload_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'physics'}</t>
+          <t>physics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Physics'}</t>
+          <t>Physics</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'biology'}</t>
+          <t>biology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Biology'}</t>
+          <t>Biology</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chemistry'}</t>
+          <t>chemistry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Chemistry'}</t>
+          <t>Chemistry</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mathematics'}</t>
+          <t>mathematics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mathematics'}</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'school-wide'}</t>
+          <t>school-wide</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'School-Wide'}</t>
+          <t>School-Wide</t>
         </is>
       </c>
     </row>
